--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484319_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484319_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8463</v>
+        <v>6.0141</v>
       </c>
       <c r="E2" t="n">
-        <v>5.001</v>
+        <v>5.122</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8453</v>
+        <v>0.892</v>
       </c>
       <c r="G2" t="n">
         <v>-0.6856</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>2.6178</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0072</v>
+        <v>1.1282</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4428</v>
+        <v>1.4896</v>
       </c>
       <c r="V2" t="n">
         <v>2.7145</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. MARKOVETSKYY</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9131</v>
+        <v>3.2526</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6195</v>
+        <v>3.1867</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2936</v>
+        <v>0.0659</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1354</v>
+        <v>0.106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1903</v>
+        <v>1.1581</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0549</v>
+        <v>-1.0521</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0249</v>
+        <v>1.34</v>
       </c>
       <c r="K3" t="n">
-        <v>0.944</v>
+        <v>1.9864</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0809</v>
+        <v>-0.6465</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8895</v>
+        <v>-1.234</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7536</v>
+        <v>-0.8283</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1358</v>
+        <v>-0.4056</v>
       </c>
       <c r="P3" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.2684</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.3359</v>
+      </c>
+      <c r="U3" t="n">
+        <v>-0.0675</v>
+      </c>
+      <c r="V3" t="n">
+        <v>2.6596</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.6596</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1.1721</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.1721</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.8911</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.2122</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.6788999999999999</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.8865</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.5545</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0.3321</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>V. MARKOVETSKYY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9253</v>
+        <v>2.6301</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2679</v>
+        <v>1.5272</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3426</v>
+        <v>1.1029</v>
       </c>
       <c r="G4" t="n">
-        <v>0.106</v>
+        <v>0.1354</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1581</v>
+        <v>0.1903</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0521</v>
+        <v>-0.0549</v>
       </c>
       <c r="J4" t="n">
-        <v>1.34</v>
+        <v>1.0249</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9864</v>
+        <v>0.944</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6465</v>
+        <v>0.0809</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.234</v>
+        <v>-0.8895</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8283</v>
+        <v>-0.7536</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4056</v>
+        <v>-0.1358</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3674</v>
+        <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.6081</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4171</v>
+        <v>1.1199</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.476</v>
+        <v>0.4883</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6596</v>
+        <v>0.8865</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6596</v>
+        <v>0.5545</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3328</v>
+        <v>1.9483</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7544999999999999</v>
+        <v>2.6273</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0873</v>
+        <v>-0.679</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1111</v>
+        <v>-0.7042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1566</v>
+        <v>-2.3763</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.2677</v>
+        <v>1.6721</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.4166</v>
+        <v>1.0035</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9849</v>
+        <v>-0.9389</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4015</v>
+        <v>1.9424</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.6945</v>
+        <v>-1.7077</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8283</v>
+        <v>-1.4375</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1338</v>
+        <v>-0.2702</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3674</v>
+        <v>0.3907</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7581</v>
+        <v>0.3907</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3778</v>
+        <v>0.379</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6824</v>
+        <v>0.4052</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6954</v>
+        <v>-0.0262</v>
       </c>
       <c r="V5" t="n">
-        <v>3.4335</v>
+        <v>1.8828</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1052</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>1.3283</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9893</v>
+        <v>1.9344</v>
       </c>
       <c r="E6" t="n">
-        <v>1.859</v>
+        <v>-1.0984</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8697</v>
+        <v>3.0328</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7042</v>
+        <v>-1.1111</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.3763</v>
+        <v>0.1566</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6721</v>
+        <v>-1.2677</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0035</v>
+        <v>-0.4166</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9389</v>
+        <v>0.9849</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9424</v>
+        <v>-1.4015</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7077</v>
+        <v>-0.6945</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4375</v>
+        <v>-0.8283</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2702</v>
+        <v>0.1338</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3907</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.58</v>
+        <v>0.9794</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3631</v>
+        <v>0.3385</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2168</v>
+        <v>0.6409</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8828</v>
+        <v>3.4335</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>2.1052</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6642</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4232</v>
+        <v>-0.1393</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2853</v>
+        <v>0.4875</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7085</v>
+        <v>-0.6268</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4171</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3967</v>
+        <v>-0.1128</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1816</v>
+        <v>0.0207</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2152</v>
+        <v>-0.1335</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9389</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7953</v>
+        <v>-0.3436</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1436</v>
+        <v>-0.4602</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5536</v>
+        <v>-2.0873</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.189</v>
+        <v>-0.6441</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3646</v>
+        <v>-1.4431</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4702</v>
+        <v>0.1054</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4298</v>
+        <v>0.738</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0239</v>
+        <v>-2.1927</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6188</v>
+        <v>-1.3822</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4051</v>
+        <v>-0.8105</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0847</v>
+        <v>1.5607</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2888</v>
+        <v>0.723</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2041</v>
+        <v>0.8376</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9434</v>
+        <v>-1.4027</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8384</v>
+        <v>-0.4339</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.105</v>
+        <v>-0.9688</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7737</v>
@@ -1156,13 +1156,13 @@
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4815</v>
+        <v>0.0592</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5309</v>
+        <v>-0.1265</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0495</v>
+        <v>0.1856</v>
       </c>
       <c r="V9" t="n">
         <v>3.6559</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8114</v>
+        <v>-1.8844</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7792</v>
+        <v>-0.7953</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0322</v>
+        <v>-1.0891</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.0873</v>
+        <v>-0.5536</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.6441</v>
+        <v>-0.189</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4431</v>
+        <v>-0.3646</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1054</v>
+        <v>0.4702</v>
       </c>
       <c r="K10" t="n">
-        <v>0.738</v>
+        <v>0.4298</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6326000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1927</v>
+        <v>-1.0239</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3822</v>
+        <v>-0.6188</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8105</v>
+        <v>-0.4051</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4468</v>
+        <v>-0.0303</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7125</v>
+        <v>-0.2888</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2657</v>
+        <v>0.2586</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3666</v>
+        <v>-5.4207</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9153</v>
+        <v>-4.7242</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4514</v>
+        <v>-0.6965</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3966</v>
@@ -1312,13 +1312,13 @@
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1202</v>
+        <v>1.0661</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4914</v>
+        <v>0.6824</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6288</v>
+        <v>0.3837</v>
       </c>
       <c r="V11" t="n">
         <v>-0.3321</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.523299999999997</v>
+        <v>6.128500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.950000000000001</v>
+        <v>5.555300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5731999999999999</v>
+        <v>0.5731999999999996</v>
       </c>
       <c r="G12" t="n">
         <v>-12.4878</v>
@@ -1369,7 +1369,7 @@
         <v>4.2387</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005999999999999839</v>
+        <v>0.005999999999999867</v>
       </c>
       <c r="M12" t="n">
         <v>-16.7327</v>
@@ -1390,13 +1390,13 @@
         <v>12.6974</v>
       </c>
       <c r="S12" t="n">
-        <v>8.790400000000002</v>
+        <v>9.3956</v>
       </c>
       <c r="T12" t="n">
-        <v>4.7334</v>
+        <v>5.338500000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>4.0572</v>
+        <v>4.0571</v>
       </c>
       <c r="V12" t="n">
         <v>13.1276</v>
@@ -1405,7 +1405,7 @@
         <v>12.5762</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5515000000000001</v>
+        <v>0.5514999999999997</v>
       </c>
     </row>
     <row r="13">
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.5934</v>
+        <v>2.8968</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7983</v>
+        <v>1.1017</v>
       </c>
       <c r="F13" t="n">
         <v>1.7951</v>
@@ -1468,10 +1468,10 @@
         <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7484</v>
+        <v>-0.4451</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6657</v>
+        <v>-0.3624</v>
       </c>
       <c r="U13" t="n">
         <v>-0.08260000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7184</v>
+        <v>0.9548</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1273</v>
+        <v>1.4195</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4089</v>
+        <v>-0.4647</v>
       </c>
       <c r="G14" t="n">
         <v>2.9545</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6388</v>
+        <v>-1.4025</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0906</v>
+        <v>-0.7984</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5483</v>
+        <v>-0.6041</v>
       </c>
       <c r="V14" t="n">
         <v>-2.16</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9757</v>
+        <v>0.8824</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2363</v>
+        <v>2.0341</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2607</v>
+        <v>-1.1517</v>
       </c>
       <c r="G15" t="n">
         <v>1.4689</v>
@@ -1624,13 +1624,13 @@
         <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2212</v>
+        <v>0.1279</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5531</v>
+        <v>0.3508</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3318</v>
+        <v>-0.2229</v>
       </c>
       <c r="V15" t="n">
         <v>-1.4959</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>A. ABELLO GIRVÉS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6552</v>
+        <v>0.4881</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0906</v>
+        <v>-1.1704</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4354</v>
+        <v>1.6585</v>
       </c>
       <c r="G16" t="n">
-        <v>4.1344</v>
+        <v>3.0956</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9918</v>
+        <v>1.6396</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1425</v>
+        <v>1.456</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3637</v>
+        <v>3.1158</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7601</v>
+        <v>1.659</v>
       </c>
       <c r="L16" t="n">
-        <v>2.6036</v>
+        <v>1.4568</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2293</v>
+        <v>-0.0202</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7682</v>
+        <v>-0.0194</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5389</v>
+        <v>-0.0008</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9534</v>
+        <v>2.1488</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2669</v>
+        <v>-1.494</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3798</v>
+        <v>-0.6918</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1129</v>
+        <v>-0.8021</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7693</v>
+        <v>-0.3321</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0466</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. ABELLO GIRVÉS</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1783</v>
+        <v>0.2858</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3726</v>
+        <v>1.585</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5509</v>
+        <v>-1.2992</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0956</v>
+        <v>4.1344</v>
       </c>
       <c r="H17" t="n">
-        <v>1.6396</v>
+        <v>0.9918</v>
       </c>
       <c r="I17" t="n">
-        <v>1.456</v>
+        <v>3.1425</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1158</v>
+        <v>4.3637</v>
       </c>
       <c r="K17" t="n">
-        <v>1.659</v>
+        <v>1.7601</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4568</v>
+        <v>2.6036</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0202</v>
+        <v>-0.2293</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0194</v>
+        <v>-0.7682</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0008</v>
+        <v>0.5389</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8038</v>
+        <v>-0.1025</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8941</v>
+        <v>-0.1257</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9097</v>
+        <v>0.0233</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3321</v>
+        <v>-2.7693</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6642</v>
+        <v>0.2772</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3321</v>
+        <v>-3.0466</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1813</v>
+        <v>-0.8521</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2073</v>
+        <v>-0.904</v>
       </c>
       <c r="F18" t="n">
-        <v>0.026</v>
+        <v>0.0518</v>
       </c>
       <c r="G18" t="n">
         <v>0.8054</v>
@@ -1858,13 +1858,13 @@
         <v>2.1488</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.6629</v>
+        <v>-1.3337</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1362</v>
+        <v>-0.8328</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5268</v>
+        <v>-0.5009</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4959</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6229</v>
+        <v>-1.3598</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4641</v>
+        <v>-1.363</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1588</v>
+        <v>0.0032</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8269</v>
@@ -1936,13 +1936,13 @@
         <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7262</v>
+        <v>-1.463</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1967</v>
+        <v>-1.0956</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5295</v>
+        <v>-0.3674</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2186</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.402</v>
+        <v>-2.4052</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2319</v>
+        <v>-0.9487</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1702</v>
+        <v>-1.4565</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5693</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1011</v>
+        <v>-0.2793</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.6703</v>
+        <v>0.8776</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4102</v>
+        <v>1.497</v>
       </c>
       <c r="K20" t="n">
-        <v>0.4502</v>
+        <v>0.3492</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8604</v>
+        <v>1.1478</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1591</v>
+        <v>-0.8988</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3492</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8099</v>
+        <v>-0.2702</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0867</v>
+        <v>-0.7848000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0989</v>
+        <v>-0.1602</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9878</v>
+        <v>-0.6246</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2772</v>
+        <v>-1.8279</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9652</v>
+        <v>-2.4344</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4542</v>
+        <v>-1.5352</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.511</v>
+        <v>-0.8992</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5983000000000001</v>
+        <v>-2.5693</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2793</v>
+        <v>0.1011</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8776</v>
+        <v>-2.6703</v>
       </c>
       <c r="J21" t="n">
-        <v>1.497</v>
+        <v>-1.4102</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3492</v>
+        <v>0.4502</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1478</v>
+        <v>-1.8604</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8988</v>
+        <v>-1.1591</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.3492</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2702</v>
+        <v>-0.8099</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3449</v>
+        <v>-1.119</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6657</v>
+        <v>-0.4023</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6791</v>
+        <v>-0.7168</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.8279</v>
+        <v>0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4729</v>
+        <v>-3.3057</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0957</v>
+        <v>-0.7923</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3772</v>
+        <v>-2.5134</v>
       </c>
       <c r="G22" t="n">
         <v>0.3132</v>
@@ -2170,13 +2170,13 @@
         <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2669</v>
+        <v>-0.0998</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2421</v>
+        <v>0.0613</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0248</v>
+        <v>-0.161</v>
       </c>
       <c r="V22" t="n">
         <v>-3.3238</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.523300000000001</v>
+        <v>-4.8493</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5732999999999995</v>
+        <v>-0.5732999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.950200000000001</v>
+        <v>-4.2761</v>
       </c>
       <c r="G23" t="n">
         <v>12.488</v>
@@ -2218,7 +2218,7 @@
         <v>5.741999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>6.745900000000002</v>
+        <v>6.745900000000001</v>
       </c>
       <c r="J23" t="n">
         <v>16.7326</v>
@@ -2230,13 +2230,13 @@
         <v>6.751900000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.244699999999999</v>
+        <v>-4.2447</v>
       </c>
       <c r="N23" t="n">
         <v>-4.238799999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.006000000000000116</v>
+        <v>-0.005999999999999894</v>
       </c>
       <c r="P23" t="n">
         <v>3.9069</v>
@@ -2248,19 +2248,19 @@
         <v>16.6042</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.7905</v>
+        <v>-8.1165</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.057099999999999</v>
+        <v>-4.0571</v>
       </c>
       <c r="U23" t="n">
-        <v>-4.733300000000001</v>
+        <v>-4.0591</v>
       </c>
       <c r="V23" t="n">
         <v>-13.1277</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.5517000000000003</v>
+        <v>-0.5517000000000002</v>
       </c>
       <c r="X23" t="n">
         <v>-12.5763</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484319_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484319_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,31 +570,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0141</v>
+        <v>5.4071</v>
       </c>
       <c r="E2" t="n">
-        <v>5.122</v>
+        <v>4.5151</v>
       </c>
       <c r="F2" t="n">
         <v>0.892</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6856</v>
+        <v>-1.2926</v>
       </c>
       <c r="H2" t="n">
         <v>-0.4152</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2704</v>
+        <v>-0.8774</v>
       </c>
       <c r="J2" t="n">
-        <v>2.256</v>
+        <v>1.649</v>
       </c>
       <c r="K2" t="n">
         <v>1.5809</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6751</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="M2" t="n">
         <v>-2.9417</v>
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.6642</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,11 +964,16 @@
       <c r="X6" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +985,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1393</v>
+        <v>0.607</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4875</v>
+        <v>0.607</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6268</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4171</v>
+        <v>0.607</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.499</v>
+        <v>0.607</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6622</v>
+        <v>0.607</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0819</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5803</v>
+        <v>0.607</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0793</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0793</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1128</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0207</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1335</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1016,12 +1046,17 @@
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. ANDUJAR MASCARO</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.1393</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3436</v>
+        <v>0.4875</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4602</v>
+        <v>-0.6268</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0873</v>
+        <v>-0.4171</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6441</v>
+        <v>0.0819</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4431</v>
+        <v>-0.499</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1054</v>
+        <v>0.6622</v>
       </c>
       <c r="K8" t="n">
-        <v>0.738</v>
+        <v>0.0819</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6326000000000001</v>
+        <v>0.5803</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1927</v>
+        <v>-1.0793</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3822</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8105</v>
+        <v>-1.0793</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5607</v>
+        <v>-0.1128</v>
       </c>
       <c r="T8" t="n">
-        <v>0.723</v>
+        <v>0.0207</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8376</v>
+        <v>-0.1335</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>L. ANDUJAR MASCARO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4027</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4339</v>
+        <v>-0.3436</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9688</v>
+        <v>-0.4602</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.7737</v>
+        <v>-2.0873</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2251</v>
+        <v>-0.6441</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5486</v>
+        <v>-1.4431</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0565</v>
+        <v>0.1054</v>
       </c>
       <c r="K9" t="n">
         <v>0.738</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7945</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7172</v>
+        <v>-2.1927</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9631999999999999</v>
+        <v>-1.3822</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.754</v>
+        <v>-0.8105</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.3441</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.9069</v>
+        <v>-1.1721</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0592</v>
+        <v>1.5607</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1265</v>
+        <v>0.723</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1856</v>
+        <v>0.8376</v>
       </c>
       <c r="V9" t="n">
-        <v>3.6559</v>
+        <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6559</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8844</v>
+        <v>-1.4027</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7953</v>
+        <v>-0.4339</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0891</v>
+        <v>-0.9688</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5536</v>
+        <v>-2.7737</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.189</v>
+        <v>-0.2251</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3646</v>
+        <v>-2.5486</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4702</v>
+        <v>-0.0565</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4298</v>
+        <v>0.738</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-0.7945</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0239</v>
+        <v>-2.7172</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6188</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4051</v>
+        <v>-1.754</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1953</v>
+        <v>-2.3441</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0303</v>
+        <v>0.0592</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2888</v>
+        <v>-0.1265</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2586</v>
+        <v>0.1856</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4959</v>
+        <v>3.6559</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>3.6559</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. NDOYE</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4207</v>
+        <v>-1.8844</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7242</v>
+        <v>-0.7953</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6965</v>
+        <v>-1.0891</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.3966</v>
+        <v>-0.5536</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.479</v>
+        <v>-0.189</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9177</v>
+        <v>-0.3646</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1444</v>
+        <v>0.4702</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.3063</v>
+        <v>0.4298</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1619</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2522</v>
+        <v>-1.0239</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1727</v>
+        <v>-0.6188</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0795</v>
+        <v>-0.4051</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7581</v>
+        <v>0.1953</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
         <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0661</v>
+        <v>-0.0303</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6824</v>
+        <v>-0.2888</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3837</v>
+        <v>0.2586</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3321</v>
+        <v>-1.4959</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. NDOYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,301 +1400,317 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.128500000000001</v>
+        <v>-5.4207</v>
       </c>
       <c r="E12" t="n">
-        <v>5.555300000000001</v>
+        <v>-4.7242</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5731999999999996</v>
+        <v>-0.6965</v>
       </c>
       <c r="G12" t="n">
-        <v>-12.4878</v>
+        <v>-4.3966</v>
       </c>
       <c r="H12" t="n">
-        <v>-5.7418</v>
+        <v>-3.479</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.746</v>
+        <v>-0.9177</v>
       </c>
       <c r="J12" t="n">
-        <v>4.2447</v>
+        <v>-2.1444</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2387</v>
+        <v>-2.3063</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005999999999999867</v>
+        <v>0.1619</v>
       </c>
       <c r="M12" t="n">
-        <v>-16.7327</v>
+        <v>-2.2522</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.9808</v>
+        <v>-1.1727</v>
       </c>
       <c r="O12" t="n">
-        <v>-6.7517</v>
+        <v>-1.0795</v>
       </c>
       <c r="P12" t="n">
-        <v>-3.9069</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q12" t="n">
-        <v>-16.6042</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
-        <v>12.6974</v>
+        <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>9.3956</v>
+        <v>1.0661</v>
       </c>
       <c r="T12" t="n">
-        <v>5.338500000000001</v>
+        <v>0.6824</v>
       </c>
       <c r="U12" t="n">
-        <v>4.0571</v>
+        <v>0.3837</v>
       </c>
       <c r="V12" t="n">
-        <v>13.1276</v>
+        <v>-0.3321</v>
       </c>
       <c r="W12" t="n">
-        <v>12.5762</v>
+        <v>-0.3321</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5514999999999997</v>
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. IBORRA BARRERA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8968</v>
+        <v>6.128500000000003</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1017</v>
+        <v>5.555400000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7951</v>
+        <v>0.5732</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5139</v>
+        <v>-12.4878</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8319</v>
+        <v>-5.7418</v>
       </c>
       <c r="I13" t="n">
-        <v>3.3458</v>
+        <v>-6.746</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1989</v>
+        <v>4.244700000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2034</v>
+        <v>4.2387</v>
       </c>
       <c r="L13" t="n">
-        <v>2.4023</v>
+        <v>0.005999999999999867</v>
       </c>
       <c r="M13" t="n">
-        <v>0.315</v>
+        <v>-16.7327</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-9.980800000000002</v>
       </c>
       <c r="O13" t="n">
-        <v>0.9435</v>
+        <v>-6.7517</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>-3.9069</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>-16.6042</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5627</v>
+        <v>12.6974</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4451</v>
+        <v>9.3956</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3624</v>
+        <v>5.338500000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.08260000000000001</v>
+        <v>4.057099999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2186</v>
+        <v>13.1276</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2186</v>
+        <v>12.5762</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
-      </c>
+        <v>0.5514999999999997</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. VILAR FERNANDEZ</t>
+          <t>S. IBORRA BARRERA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9548</v>
+        <v>2.8968</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4195</v>
+        <v>1.1017</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4647</v>
+        <v>1.7951</v>
       </c>
       <c r="G14" t="n">
-        <v>2.9545</v>
+        <v>2.5139</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5909</v>
+        <v>-0.8319</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3636</v>
+        <v>3.3458</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8587</v>
+        <v>2.1989</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9547</v>
+        <v>-0.2034</v>
       </c>
       <c r="L14" t="n">
-        <v>0.9041</v>
+        <v>2.4023</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9042</v>
+        <v>0.315</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3638</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5405</v>
+        <v>0.9435</v>
       </c>
       <c r="P14" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.5627</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.5395</v>
-      </c>
       <c r="S14" t="n">
-        <v>-1.4025</v>
+        <v>-0.4451</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7984</v>
+        <v>-0.3624</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6041</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.16</v>
+        <v>1.2186</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SUAREZ CANOSA</t>
+          <t>P. CARRIÓN SORIANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8824</v>
+        <v>1.821</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0341</v>
+        <v>1.821</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1517</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4689</v>
+        <v>1.821</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1361</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>1.605</v>
+        <v>1.821</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6833</v>
+        <v>1.821</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3479</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3354</v>
+        <v>1.821</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2144</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.484</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2696</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1279</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3508</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2229</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1650,621 +1721,906 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4881</v>
+        <v>1.214</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1704</v>
+        <v>1.214</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6585</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0956</v>
+        <v>1.214</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6396</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1.456</v>
+        <v>1.214</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1158</v>
+        <v>1.214</v>
       </c>
       <c r="K16" t="n">
-        <v>1.659</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4568</v>
+        <v>1.214</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0202</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0194</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0008</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.494</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6918</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8021</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. PUERTAS GARCIA</t>
+          <t>F. VILAR FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C17" t="n">
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2858</v>
+        <v>0.9548</v>
       </c>
       <c r="E17" t="n">
-        <v>1.585</v>
+        <v>1.4195</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2992</v>
+        <v>-0.4647</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1344</v>
+        <v>2.9545</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9918</v>
+        <v>2.5909</v>
       </c>
       <c r="I17" t="n">
-        <v>3.1425</v>
+        <v>0.3636</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3637</v>
+        <v>3.8587</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7601</v>
+        <v>2.9547</v>
       </c>
       <c r="L17" t="n">
-        <v>2.6036</v>
+        <v>0.9041</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2293</v>
+        <v>-0.9042</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7682</v>
+        <v>-0.3638</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5389</v>
+        <v>-0.5405</v>
       </c>
       <c r="P17" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.9301</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1025</v>
+        <v>-1.4025</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1257</v>
+        <v>-0.7984</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0233</v>
+        <v>-0.6041</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7693</v>
+        <v>-2.16</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X17" t="n">
-        <v>-3.0466</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. JAIME BATLLE</t>
+          <t>M. SUAREZ CANOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8521</v>
+        <v>0.8824</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.904</v>
+        <v>2.0341</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0518</v>
+        <v>-1.1517</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8054</v>
+        <v>1.4689</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2904</v>
+        <v>-0.1361</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.485</v>
+        <v>1.605</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5697</v>
+        <v>1.6833</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5145</v>
+        <v>0.3479</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0553</v>
+        <v>1.3354</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7643</v>
+        <v>-0.2144</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2241</v>
+        <v>-0.484</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5403</v>
+        <v>0.2696</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.1488</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3337</v>
+        <v>0.1279</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8328</v>
+        <v>0.3508</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5009</v>
+        <v>-0.2229</v>
       </c>
       <c r="V18" t="n">
         <v>-1.4959</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8317</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GALVE NAVARRO</t>
+          <t>A. PUERTAS GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3598</v>
+        <v>0.2858</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.363</v>
+        <v>1.585</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0032</v>
+        <v>-1.2992</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8269</v>
+        <v>4.1344</v>
       </c>
       <c r="H19" t="n">
-        <v>0.008399999999999999</v>
+        <v>0.9918</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8354</v>
+        <v>3.1425</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2674</v>
+        <v>4.3637</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4323</v>
+        <v>1.7601</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6998</v>
+        <v>2.6036</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5595</v>
+        <v>-0.2293</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4239</v>
+        <v>-0.7682</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1356</v>
+        <v>0.5389</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1488</v>
+        <v>1.9534</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.463</v>
+        <v>-0.1025</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0956</v>
+        <v>-0.1257</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3674</v>
+        <v>0.0233</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>-2.7693</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-3.0466</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. CARRIÓN SORIANO</t>
+          <t>A. ABELLO GIRVES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4052</v>
+        <v>-0.7258</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9487</v>
+        <v>-2.3844</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4565</v>
+        <v>1.6585</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5983000000000001</v>
+        <v>1.8816</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2793</v>
+        <v>1.6396</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8776</v>
+        <v>0.242</v>
       </c>
       <c r="J20" t="n">
-        <v>1.497</v>
+        <v>1.9018</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3492</v>
+        <v>1.659</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1478</v>
+        <v>0.2428</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8988</v>
+        <v>-0.0202</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.0194</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2702</v>
+        <v>-0.0008</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7848000000000001</v>
+        <v>-1.494</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1602</v>
+        <v>-0.6918</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6246</v>
+        <v>-0.8021</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-0.3321</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>-0.6642</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4959</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ISERN CASES</t>
+          <t>A. JAIME BATLLE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4344</v>
+        <v>-0.8521</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5352</v>
+        <v>-0.904</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8992</v>
+        <v>0.0518</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5693</v>
+        <v>0.8054</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1011</v>
+        <v>1.2904</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6703</v>
+        <v>-0.485</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4102</v>
+        <v>1.5697</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4502</v>
+        <v>1.5145</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.8604</v>
+        <v>0.0553</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1591</v>
+        <v>-0.7643</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3492</v>
+        <v>-0.2241</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.8099</v>
+        <v>-0.5403</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.119</v>
+        <v>-1.3337</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4023</v>
+        <v>-0.8328</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7168</v>
+        <v>-0.5009</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>-0.6642</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. HERETER MARCHANTE</t>
+          <t>J. GALVE NAVARRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3057</v>
+        <v>-1.3598</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7923</v>
+        <v>-1.363</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5134</v>
+        <v>0.0032</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3132</v>
+        <v>-0.8269</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3671</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0539</v>
+        <v>-0.8354</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1231</v>
+        <v>-0.2674</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7163</v>
+        <v>0.4323</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.6998</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1901</v>
+        <v>-0.5595</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3492</v>
+        <v>-0.4239</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5393</v>
+        <v>-0.1356</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.1953</v>
+        <v>2.1488</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>2.1488</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0998</v>
+        <v>-1.463</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0613</v>
+        <v>-1.0956</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.161</v>
+        <v>-0.3674</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.3238</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.3238</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. ISERN CASES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SESE</t>
+          <t>SESE A</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.8493</v>
+        <v>-2.4344</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5732999999999999</v>
+        <v>-1.5352</v>
       </c>
       <c r="F23" t="n">
+        <v>-0.8992</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.5693</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1011</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-2.6703</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-1.4102</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.4502</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.8604</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-1.1591</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-0.8099</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-1.119</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.4023</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.7168</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>G. HERETER MARCHANTE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-3.3057</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-0.7923</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.5134</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-0.0539</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.1231</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.7163</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-0.5931999999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.3492</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5393</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-0.1953</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.0998</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.0613</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.161</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-3.3238</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-3.3238</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P. CARRION SORIANO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.2261</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-2.7696</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-1.4565</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1.2227</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.2793</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.9433</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-0.3239</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6731</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.8988</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6284999999999999</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.2702</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.7848000000000001</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.1602</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.6246</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484319_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>SESE A</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.8491</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-0.5732000000000004</v>
+      </c>
+      <c r="F26" t="n">
         <v>-4.2761</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G26" t="n">
         <v>12.488</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H26" t="n">
         <v>5.741999999999999</v>
       </c>
-      <c r="I23" t="n">
-        <v>6.745900000000001</v>
-      </c>
-      <c r="J23" t="n">
-        <v>16.7326</v>
-      </c>
-      <c r="K23" t="n">
+      <c r="I26" t="n">
+        <v>6.746000000000001</v>
+      </c>
+      <c r="J26" t="n">
+        <v>16.7327</v>
+      </c>
+      <c r="K26" t="n">
         <v>9.9808</v>
       </c>
-      <c r="L23" t="n">
-        <v>6.751900000000001</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="L26" t="n">
+        <v>6.752000000000001</v>
+      </c>
+      <c r="M26" t="n">
         <v>-4.2447</v>
       </c>
-      <c r="N23" t="n">
-        <v>-4.238799999999999</v>
-      </c>
-      <c r="O23" t="n">
-        <v>-0.005999999999999894</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="N26" t="n">
+        <v>-4.2388</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.006000000000000005</v>
+      </c>
+      <c r="P26" t="n">
         <v>3.9069</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q26" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R26" t="n">
         <v>16.6042</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S26" t="n">
         <v>-8.1165</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T26" t="n">
         <v>-4.0571</v>
       </c>
-      <c r="U23" t="n">
+      <c r="U26" t="n">
         <v>-4.0591</v>
       </c>
-      <c r="V23" t="n">
+      <c r="V26" t="n">
         <v>-13.1277</v>
       </c>
-      <c r="W23" t="n">
-        <v>-0.5517000000000002</v>
-      </c>
-      <c r="X23" t="n">
+      <c r="W26" t="n">
+        <v>-0.5517000000000003</v>
+      </c>
+      <c r="X26" t="n">
         <v>-12.5763</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
